--- a/data/0402A_20260826.xlsx
+++ b/data/0402A_20260826.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>6382208854</t>
+          <t>6460722899</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.71%</t>
+          <t>98.30%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.66%</t>
+          <t>8.73%</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.56%</t>
+          <t>7.46%</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>6.35%</t>
         </is>
       </c>
     </row>
@@ -587,12 +587,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19,100</t>
+          <t>21,100</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.65%</t>
+          <t>5.12%</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4.56%</t>
+          <t>4.73%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.40%</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.32%</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -874,22 +874,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADI US</t>
+          <t>COHR US</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analog Devices Inc</t>
+          <t>Coherent Corp</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10,700</t>
+          <t>14,400</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COHR US</t>
+          <t>ADI US</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Coherent Corp</t>
+          <t>Analog Devices Inc</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>14,400</t>
+          <t>10,700</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -928,22 +928,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML US</t>
+          <t>LITE US</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Lumentum Holdings Inc</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>4,400</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -955,22 +955,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LITE US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4,400</t>
+          <t>15,700</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -982,22 +982,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>ASML US</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15,700</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1063,22 +1063,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TSM US</t>
+          <t>CDNS US</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Co Ltd</t>
+          <t>Cadence Design Systems Inc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>9,600</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1090,22 +1090,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CDNS US</t>
+          <t>TSM US</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cadence Design Systems Inc</t>
+          <t>Taiwan Semiconductor Manufacturing Co Ltd</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9,600</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1225,22 +1225,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MCHP US</t>
+          <t>AXON US</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Microchip Technology Inc</t>
+          <t>Axon Enterprise Inc</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>33,200</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1252,22 +1252,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AXON US</t>
+          <t>MCHP US</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Axon Enterprise Inc</t>
+          <t>Microchip Technology Inc</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>33,200</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1387,22 +1387,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TER US</t>
+          <t>CLS US</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Teradyne Inc</t>
+          <t>Celestica Inc</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5,100</t>
+          <t>6,100</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1414,22 +1414,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CLS US</t>
+          <t>TER US</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Celestica Inc</t>
+          <t>Teradyne Inc</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>5,100</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1468,22 +1468,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SHOP US</t>
+          <t>CIEN US</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Ciena Corp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11,600</t>
+          <t>4,600</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1495,22 +1495,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MDB US</t>
+          <t>SHOP US</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MongoDB Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>11,600</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1522,22 +1522,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CIEN US</t>
+          <t>MDB US</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ciena Corp</t>
+          <t>MongoDB Inc</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4,600</t>
+          <t>4,300</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
